--- a/testdata/lead/bulk_upload/sneha_contact.xlsx
+++ b/testdata/lead/bulk_upload/sneha_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bhaanumati Chaturvedi</v>
+        <v>Ekaparnika Kapoor</v>
       </c>
       <c r="B2" t="str">
-        <v>bhaanumati.chaturvedi658@gmail.com</v>
+        <v>ekaparnika.kapoor155@gmail.com</v>
       </c>
       <c r="C2">
-        <v>8836868710</v>
+        <v>9663910596</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jyotsana Khatri</v>
+        <v>Elakshi Mahajan</v>
       </c>
       <c r="B3" t="str">
-        <v>jyotsana.khatri122@gmail.com</v>
+        <v>elakshi.mahajan452@gmail.com</v>
       </c>
       <c r="C3">
-        <v>8729429006</v>
+        <v>9873308370</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Agrata Khan</v>
+        <v>Amodini Pandey</v>
       </c>
       <c r="B4" t="str">
-        <v>agrata.khan229@gmail.com</v>
+        <v>amodini.pandey842@gmail.com</v>
       </c>
       <c r="C4">
-        <v>8719995591</v>
+        <v>8737775486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Chiranjeeve Kaul-Dutta</v>
+        <v>Ravi Bhattathiri</v>
       </c>
       <c r="B5" t="str">
-        <v>chiranjeeve.kauldutta208@gmail.com</v>
+        <v>ravi.bhattathiri200@gmail.com</v>
       </c>
       <c r="C5">
-        <v>9973701249</v>
+        <v>9936199143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Amritambu Acharya</v>
+        <v>Darshan Dhawan</v>
       </c>
       <c r="B6" t="str">
-        <v>amritambu.acharya470@gmail.com</v>
+        <v>darshan.dhawan999@gmail.com</v>
       </c>
       <c r="C6">
-        <v>8711531700</v>
+        <v>9821466409</v>
       </c>
     </row>
   </sheetData>
